--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -962,6 +962,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1212,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1373,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2032,6 +2033,66 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>U10-06.1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Admin console + AI model routing</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Admin model switcher -- change model-per-task at runtime</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Runtime, DB-backed override of MODEL_ROUTES per AI task from the super-admin console (no redeploy). model_for() reads an override layer first: env -&gt; DB override -&gt; MODEL_ROUTES -&gt; default. Admin picks the model per task from the MODELS catalog; the change is audited. Pairs with the AI quality dashboard (E3-10.2) so the effect of a switch is visible.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>E3-01.2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Added 2026-08-25. Deferred from the Epic 3 model-routing discussion to Epic 10 per founder. TODAY models change only via config.py MODELS + MODEL_ROUTE_&lt;TASK&gt; env override (needs a redeploy). Sibling to U10-00.4 AI provider keys.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Epic 10 S6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2093,6 +2093,66 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>U10-06.2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Admin console + STT/TTS config</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sarvam STT + TTS model/mode/voice admin config</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Runtime, DB-backed admin config for the Sarvam voice stack (no redeploy): STT model (saaras:v3 / v4), STT mode (transcribe / translate / codemix -- codemix best for Tanglish), and Bulbul TTS voice model + speaker. Read by the integrations/stt.py + TTS layer, override order env -&gt; DB -&gt; default. Sibling to U10-06.1 (LLM model switcher) and U10-00.4 (AI provider keys).</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>E3-07.1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Added 2026-08-25 per founder: STT is Sarvam-only; make Sarvam model/mode + Bulbul voice admin-configurable here rather than in Epic 3. Today SARVAM_STT_MODEL + mode are env/hardcoded (saaras:v3, mode=translate).</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Epic 10 S6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2153,422 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>U10-01.1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Admin / Tenant 360</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cross-tenant search</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GET /api/admin/search?q= -- find a workspace (name/id) or user (name/email/phone/id) across all tenants; returns tenants + users with workspace names attached. Gated by get_platform_admin, read-only.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>routers/admin_tenant360.py</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>U10-01.2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Admin / Tenant 360</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Tenant 360 aggregate endpoint</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GET /api/admin/tenants/{id}/360 -- one consolidated per-workspace payload: plan+entitlements, entity counts (users/decisions/tasks/workflows/contacts/invoices/complaints), members, AI spend (30d+all-time), recent activity, health. Parallel queries via asyncio.gather.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>U10-01.1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>routers/admin_tenant360.py</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>U10-01.3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Admin / Tenant 360</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Per-tenant members + roles</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Members list (name/email/role/suspended/created) + active-membership count in the 360 payload.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>U10-01.2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>part of 360</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>U10-01.4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Admin / Tenant 360</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Per-tenant AI spend</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AI spend rollup (calls/tokens/cost) for last-30d and all-time from usage_events, in the 360 payload.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>U10-01.2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>part of 360</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>U10-01.5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Admin / Tenant 360</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Per-tenant config + entitlements view</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plan, seat limit(+override), feature_flags, usage_quotas, AI consent, GST, industry/region/currency surfaced in the 360.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>U10-01.2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>part of 360</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>U10-01.6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Admin / Tenant 360</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Activity timeline + health signals</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Recent db.activity timeline (20) + health (last_activity, suspended, ai_consent) in the 360.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>U10-01.2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>part of 360</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>U10-01.7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Admin portal</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Tenant 360 tab (search + drill-in)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>New AdminPortal tab: search box -&gt; workspace/user results -&gt; click to open the consolidated 360 view (counts grid, spend, entitlements, health, members, activity). Self-contained Tenant360Section.js matching the admin dark theme.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>U10-01.2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/admin/Tenant360Section.js</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2197,7 +2197,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>routers/admin_tenant360.py</t>
@@ -2566,6 +2565,362 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Epic 10 S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>U10-02.1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Admin / Impersonation</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Impersonation token + session model</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>create_impersonation_token (core/security): a short-lived target-user JWT with an `imp` claim {admin, session_id, read_only}, exp&lt;=240m, bound to an impersonation_sessions record {admin_email, tenant, target, read_only, reason, granted/expires, revoked}.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>core/security.py</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Epic 10 S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U10-02.2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>core/deps</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>get_current_user impersonation recognition</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>get_current_user detects the `imp` claim, verifies the impersonation_sessions record is live (not revoked / not expired) -- session-based revocation replaces the jti check -- and loads the target user with membership projection.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>U10-02.1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>core/deps.py</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Epic 10 S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>U10-02.3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>core/deps</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Read-first enforcement</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>When the session is read_only, any mutating request (non GET/HEAD/OPTIONS) is blocked with 403 'writes are blocked'. Verified end-to-end: GET reads as tenant, POST -&gt; 403, revoke -&gt; 401.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>U10-02.2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>core/deps.py</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Epic 10 S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>U10-02.4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Admin / Impersonation</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Grant / list / revoke endpoints + audit</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>POST /admin/tenants/{id}/impersonate (reason/target/minutes/read_only) -&gt; session+token; GET /admin/impersonation -&gt; sessions with live/expired/revoked status; POST /admin/impersonation/{id}/revoke. Every grant+revoke written to platform_audit.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>U10-02.1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>routers/admin_impersonation.py</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Epic 10 S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>U10-02.5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Admin / Impersonation</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Impersonation flags for banner + audit</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>get_current_user stamps _impersonated_by / _read_only / _impersonation_session on the user (survives project_membership_onto_user), so /me exposes them for an in-app banner and downstream audit.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>U10-02.2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>core/deps.py + /me</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Epic 10 S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>U10-02.6</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Admin portal</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Impersonation tab + 'View as tenant'</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>New Impersonation admin tab (sessions list with status + End/revoke). 'View as tenant' button in Tenant 360 starts a 30m read-only session (audited, prompts for reason). Seamless browse-as-tenant + in-app banner noted as a follow-on UX refinement.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>U10-02.4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/admin/ImpersonationSection.js</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Epic 10 S2</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2612,7 +2612,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>core/security.py</t>
@@ -2921,6 +2920,422 @@
       <c r="L26" t="inlineStr">
         <is>
           <t>Epic 10 S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>U10-03.1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Admin / Support</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ticket model + create</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>support_tickets collection {tenant, subject, status(open/pending/resolved/closed), priority(low/normal/high/urgent), created_by(+type), assigned_admin, messages[]}. Created by admin (on a tenant's behalf) or by a tenant owner.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>routers/admin_support.py</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Epic 10 S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>U10-03.2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Admin / Support</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ticket inbox (filter + counts)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>GET /admin/tickets?status=&amp;priority=&amp;tenant_id= -&gt; newest-first list (messages omitted) + per-status counts.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>U10-03.1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>routers/admin_support.py</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Epic 10 S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>U10-03.3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Admin / Support</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ticket detail + thread</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>GET /admin/tickets/{id} -&gt; full ticket incl. message thread.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>U10-03.1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>routers/admin_support.py</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Epic 10 S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>U10-03.4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Admin / Support</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Reply + status/priority/assign</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>POST /admin/tickets/{id}/reply (adds admin msg, -&gt; pending) + PATCH /admin/tickets/{id} (status/priority/assigned_admin). Audited.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>U10-03.1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>routers/admin_support.py</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Epic 10 S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>U10-03.5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Admin / Support</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Jump to impersonation from ticket</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ticket detail 'View as tenant' starts a read-only impersonation session for the ticket's workspace (reuses S2).</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>U10-03.3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>frontend SupportDeskSection</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Epic 10 S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>U10-03.6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Support (tenant)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Tenant-facing ticket submission</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>routers/support.py: POST /api/support/tickets (owner/member raises), GET /api/support/tickets (their tickets), reply. Writes naturally blocked under read-only impersonation.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>U10-03.1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>routers/support.py</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Epic 10 S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>U10-03.7</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Admin portal</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Support desk tab</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Inbox with status filter + counts -&gt; ticket detail (thread, reply box, status/priority selects, view-as-tenant). SupportDeskSection.js.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>U10-03.2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/admin/SupportDeskSection.js</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Epic 10 S3</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2967,7 +2967,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>routers/admin_support.py</t>
@@ -3336,6 +3335,422 @@
       <c r="L33" t="inlineStr">
         <is>
           <t>Epic 10 S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>U10-04.1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Admin / Billing</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MRR &amp; revenue dashboard</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>GET /admin/billing/overview: MRR/ARR recognised from active paid plans x list price, plan distribution, all-time + 30d revenue from db.billing_events, recent payments. Razorpay/INR.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>routers/admin_billing.py</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Epic 10 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>U10-04.2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Admin / Billing</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Per-tenant plan + subscription view</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>GET /admin/billing/tenants: plan, seat-limit override, lifetime revenue, last payment, #payments per workspace.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>U10-04.1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>routers/admin_billing.py</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Epic 10 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>U10-04.3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Admin / Billing</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Razorpay reconciliation</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GET /admin/billing/reconciliation: events grouped by type, unmatched events (no tenant_id -&gt; manual queue), failed/halted list.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>U10-04.1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>routers/admin_billing.py</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Epic 10 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>U10-04.4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Admin / Billing</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Subscription lifecycle view</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Plan + last-payment + payment-count surfaced per tenant (overview + tenants); failed/halted in reconciliation.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>U10-04.2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>routers/admin_billing.py</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Epic 10 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>U10-04.5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Admin / Billing</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Manual plan override / comp</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PATCH /admin/billing/tenants/{id}/plan: set plan (grant free/comp) + seat_limit_override with a required reason; audited.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>U10-04.2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>routers/admin_billing.py</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Epic 10 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>U10-04.6</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Admin / Billing</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Per-tenant payment history</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>GET /admin/billing/tenants/{id}/payments: full billing-event history + lifetime revenue for one workspace.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>U10-04.2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>routers/admin_billing.py</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Epic 10 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>U10-04.7</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Admin portal</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Billing tab</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MRR/ARR/revenue cards, plan-mix table, reconciliation summary, per-tenant list with inline plan override. BillingSection.js (INR formatting).</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>U10-04.1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/admin/BillingSection.js</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Epic 10 S4</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3382,7 +3382,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>routers/admin_billing.py</t>
@@ -3751,6 +3750,358 @@
       <c r="L40" t="inlineStr">
         <is>
           <t>Epic 10 S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>U10-05.1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Admin / Observability</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI reliability + latency</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>GET /admin/observability/reliability?range=: error rate, degraded/fallback rate, latency p50/p95/max, breakdowns by provider (engine) + task, over 1h/24h/7d/30d.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>routers/admin_observability.py</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Epic 10 S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>U10-05.2</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Admin / Observability</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recent-errors log viewer</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>GET /admin/observability/errors: recent failed AI calls (ok=False) with task/model/engine/error(PII-redacted)/tenant/time.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>U10-05.1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>routers/admin_observability.py</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Epic 10 S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>U10-05.3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Admin / Observability</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Provider-outage timeline</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GET /admin/observability/outages: platform_alerts history, active-first, with resolved/active status + active count.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>routers/admin_observability.py</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Epic 10 S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>U10-05.4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Admin / Observability</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Error aggregation by task/provider</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Per-task + per-provider error + degraded counts in the reliability payload (the aggregation surface).</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>U10-05.1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>routers/admin_observability.py</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Epic 10 S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>U10-05.5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Admin / Observability</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Latency / slow-call signals</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Latency percentiles (p50/p95/max) overall + avg per provider/task from ai_calls.latency_ms. NOTE: rate-limit is in-memory (not persisted) -&gt; fallback/degraded rate is the reliability signal instead.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>U10-05.1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>routers/admin_observability.py</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Epic 10 S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>U10-05.6</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Admin portal</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Observability tab</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Reliability cards (calls / error rate / fallback / p95 latency) + by-provider/by-task tables + recent-errors viewer + outage timeline, with a range selector. ObservabilitySection.js.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>U10-05.1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/admin/ObservabilitySection.js</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Epic 10 S5</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Added 2026-08-25. Deferred from the Epic 3 model-routing discussion to Epic 10 per founder. TODAY models change only via config.py MODELS + MODEL_ROUTE_&lt;TASK&gt; env override (needs a redeploy). Sibling to U10-00.4 AI provider keys.</t>
+          <t>Done 2026-08-27: DB-backed override in db.platform_config, applied to sync hot paths (config._MODEL_OVERRIDES for model_for; integrations.stt._SARVAM_RUNTIME for STT model/mode). Loaded at boot + refreshed each scheduler tick so replicas converge. Verified: model_for + Sarvam hot path change with no redeploy.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Added 2026-08-25 per founder: STT is Sarvam-only; make Sarvam model/mode + Bulbul voice admin-configurable here rather than in Epic 3. Today SARVAM_STT_MODEL + mode are env/hardcoded (saaras:v3, mode=translate).</t>
+          <t>Done 2026-08-27: DB-backed override in db.platform_config, applied to sync hot paths (config._MODEL_OVERRIDES for model_for; integrations.stt._SARVAM_RUNTIME for STT model/mode). Loaded at boot + refreshed each scheduler tick so replicas converge. Verified: model_for + Sarvam hot path change with no redeploy.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3797,7 +3797,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>routers/admin_observability.py</t>
@@ -3913,7 +3912,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>routers/admin_observability.py</t>
@@ -4102,6 +4100,286 @@
       <c r="L46" t="inlineStr">
         <is>
           <t>Epic 10 S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>U10-06.3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Admin / Config</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Per-tenant feature flags</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GET/PATCH /admin/tenants/{id}/flags -&gt; tenant.feature_flags (merge). Audited.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>routers/admin_config.py</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Epic 10 S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>U10-06.4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Admin / Config</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Global feature flags</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PATCH /admin/config/flags -&gt; global_flags in db.platform_config; surfaced in GET /admin/config.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>routers/admin_config.py</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Epic 10 S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>U10-06.5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Admin / Config</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Plan-gated capabilities</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PATCH /admin/config/plan-capabilities -&gt; {plan: {cap: bool}} in platform_config.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>routers/admin_config.py</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Epic 10 S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>U10-06.6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Admin / Config</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Runtime config (thresholds)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PATCH /admin/config/runtime -&gt; free-form runtime KV merged into platform_config (budgets, thresholds).</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>routers/admin_config.py</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Epic 10 S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>U10-06.7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Admin portal</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Config &amp; Flags tab</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ConfigSection.js: Sarvam voice selects, global-flag toggles + add, and a per-task AI model-route override table (effective/default/override).</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/admin/ConfigSection.js</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Epic 10 S6</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4147,7 +4147,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>routers/admin_config.py</t>
@@ -4203,7 +4202,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>routers/admin_config.py</t>
@@ -4259,7 +4257,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>routers/admin_config.py</t>
@@ -4315,7 +4312,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>routers/admin_config.py</t>
@@ -4371,7 +4367,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>frontend/src/pages/admin/ConfigSection.js</t>
@@ -4380,6 +4375,362 @@
       <c r="L51" t="inlineStr">
         <is>
           <t>Epic 10 S6</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>U10-07.1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Admin / RBAC</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Admin roles</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>platform_admins.role in super_admin/support/billing/read_only; existing admins default to super_admin (get_platform_admin stamps it).</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>core/security.py</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Epic 10 S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>U10-07.2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Admin / RBAC</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Role enforcement</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Global read-only guard (read_only admin blocked on any non-GET) in get_platform_admin + require_admin_role(*roles) dependency (super_admin always allowed). AI-keys write gated to super_admin.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>U10-07.1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>core/security.py + routers/admin.py</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Epic 10 S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>U10-07.3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Admin / RBAC</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Admin 2FA (TOTP)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Enroll/confirm/disable reusing services.auth.totp, stored on platform_admins.two_factor; admin_login gated (requires_2fa -&gt; code) when enabled. Verified with a pyotp code + 10 backup codes.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>U10-07.1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>routers/admin_rbac.py</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Epic 10 S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>U10-07.4</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Admin / RBAC</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Admin user management</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>super_admin-only: GET/POST /admin/admins, PATCH role/active, self-demote/deactivate guard. Audited.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>U10-07.1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>routers/admin_rbac.py</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Epic 10 S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>U10-07.5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Admin / RBAC</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Session security signals</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>last_login stamped on admin login; read-only guard + full platform_audit trail; admin active/deactivate. (IP allowlist deferred.)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>U10-07.2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>routers/admin.py</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Epic 10 S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>U10-07.6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Admin portal</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Admin RBAC tab</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>AdminRbacSection.js: manage admins (add/role/deactivate, super_admin only) + own 2FA (enroll -&gt; confirm -&gt; backup codes / disable).</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>U10-07.4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/admin/AdminRbacSection.js</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Epic 10 S7</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -958,7 +958,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 10 STARTED. Sprint 0 (current state) COMPLETE (10/10): the platform super-admin console already ships -- 24 API routes + an 8-tab portal (Overview/Usage/AI-Keys/Workspaces/Users/Maintenance/Audit/Health), separate /admin auth + immutable platform_audit. Forward sprints S1-S10 planned (scope-level): tenant 360, impersonation, support desk, billing, observability, flags, admin RBAC, comms, DPDP, QA.</t>
+          <t>Epic 10 IN PROGRESS. S0 shipped + S1-S8 COMPLETE (Tenant 360, impersonation, support desk, billing, observability, feature-flags/config, admin RBAC+2FA, announcements). 8 new admin tabs + a tenant announcement banner; 60+ new routes; route fingerprint tracked via the committed API-parity baseline. Remaining: S9 (compliance/DPDP data ops) + S10 (admin polish, tests &amp; QA).</t>
         </is>
       </c>
     </row>
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4422,7 +4422,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>core/security.py</t>
@@ -4731,6 +4730,302 @@
       <c r="L57" t="inlineStr">
         <is>
           <t>Epic 10 S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>U10-08.1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Admin / Announce</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>In-app broadcast + banner model</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>announcements collection {title, body, kind(info/warning/maintenance), audience, active, dismissible, created_by}. Admin CRUD: create/list/patch/delete. Audited.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>routers/admin_announcements.py</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Epic 10 S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>U10-08.2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Admin / Announce</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Maintenance scheduling</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>starts_at/ends_at + active -&gt; _is_live() so a banner shows only in-window; scheduled maintenance banners.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>U10-08.1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>routers/admin_announcements.py</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Epic 10 S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>U10-08.3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Admin / Announce</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Targeted email to owners</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>POST /admin/announcements/{id}/email: resolve targeted workspaces -&gt; owner emails -&gt; send_email (capped 1000), audited with sent/target count.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>U10-08.1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>routers/admin_announcements.py</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Epic 10 S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>U10-08.4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Announcements (tenant)</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Audience targeting + tenant feed</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>audience all | plan:&lt;key&gt; | tenant:&lt;id&gt;; GET /api/announcements/active returns live+targeted announcements for the caller's workspace (in-app banner feed).</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>U10-08.1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>routers/admin_announcements.py</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Epic 10 S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>U10-08.5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>App + admin portal</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Announcements tab + in-app banner</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Admin Announce tab (create/enable/email/delete). Tenant AnnouncementBanner mounted in Layout: dismissible (localStorage), kind-coloured, reads /api/announcements/active.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>U10-08.4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>frontend AnnouncementsSection.js + components/AnnouncementBanner.js</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Epic 10 S8</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Admin_Console.xlsx
+++ b/docs/DecisionOS_Epic10_Admin_Console.xlsx
@@ -958,11 +958,10 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Epic 10 IN PROGRESS. S0 shipped + S1-S8 COMPLETE (Tenant 360, impersonation, support desk, billing, observability, feature-flags/config, admin RBAC+2FA, announcements). 8 new admin tabs + a tenant announcement banner; 60+ new routes; route fingerprint tracked via the committed API-parity baseline. Remaining: S9 (compliance/DPDP data ops) + S10 (admin polish, tests &amp; QA).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Epic 10 IN PROGRESS. S0 shipped + S1-S8 COMPLETE (Tenant 360, impersonation, support desk, billing, observability, feature-flags/config, admin RBAC+2FA, announcements). 8 new admin tabs + a tenant announcement banner; 60+ new routes; route fingerprint tracked via the committed API-parity baseline. Browser preview QA: full 16-tab walk-through green after a motor aggregate() coroutine fix in admin_usage (see backlog U10-QA.1). Remaining: S9 (compliance/DPDP data ops) + S10 (admin polish, tests &amp; QA).</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1374,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4777,7 +4776,6 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>routers/admin_announcements.py</t>
@@ -5026,6 +5024,62 @@
       <c r="L62" t="inlineStr">
         <is>
           <t>Epic 10 S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>U10-QA.1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Admin / Usage</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Bugfix</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Fix admin_usage motor aggregate() coroutine bug</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Split `db.usage_events.aggregate(...).to_list()` into `_cur = await db...aggregate(...); await _cur.to_list(N)` in both the per-provider and per-workspace queries. Under motor 3.x aggregate() returns a coroutine so chained .to_list() raised AttributeError -&gt; 500. Caught in browser QA walk-through of the Admin &gt; Usage tab; endpoint now returns 200 OK.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>routers/admin.py (S0 admin_usage)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Epic 10 QA fix (browser preview walk-through)</t>
         </is>
       </c>
     </row>
